--- a/artfynd/A 61417-2021 artfynd.xlsx
+++ b/artfynd/A 61417-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61417-2021 artfynd.xlsx
+++ b/artfynd/A 61417-2021 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75330796</v>
+        <v>75330797</v>
       </c>
       <c r="B2" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575533.9651669366</v>
+        <v>575516</v>
       </c>
       <c r="R2" t="n">
-        <v>7086887.003273628</v>
+        <v>7086892</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2017-10-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +767,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tallump</t>
+          <t>1 substratenheter # gammal grov, fallen torraka</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75330799</v>
+        <v>75330800</v>
       </c>
       <c r="B3" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575438.0569055985</v>
+        <v>575376</v>
       </c>
       <c r="R3" t="n">
-        <v>7087023.012432274</v>
+        <v>7087153</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,21 +857,11 @@
           <t>2017-10-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-10-03</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -903,7 +873,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>blockig, drygt 100-årig tallskog med gott om gammeltallar</t>
+          <t>blockig, drygt 100-årig tallskog med spridda gammeltallar</t>
         </is>
       </c>
       <c r="AN3" t="n">
@@ -911,7 +881,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # tallåga, bränd, gammal</t>
+          <t>1 substratenheter # tallåga, grov, yxhuggen, gammal</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -933,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>75330798</v>
+        <v>75330796</v>
       </c>
       <c r="B4" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575480.9597839924</v>
+        <v>575534</v>
       </c>
       <c r="R4" t="n">
-        <v>7086999.818690745</v>
+        <v>7086887</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1006,19 +971,9 @@
           <t>2017-10-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-10-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,7 +995,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal grov tallstock</t>
+          <t>1 substratenheter # gammal tallump</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1062,37 +1017,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>75330800</v>
+        <v>75330798</v>
       </c>
       <c r="B5" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1102,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575375.8276160299</v>
+        <v>575481</v>
       </c>
       <c r="R5" t="n">
-        <v>7087152.781184412</v>
+        <v>7087000</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,21 +1085,11 @@
           <t>2017-10-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-10-03</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1161,7 +1101,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>blockig, drygt 100-årig tallskog med spridda gammeltallar</t>
+          <t>blockig, drygt 100-årig tallskog med gott om gammeltallar</t>
         </is>
       </c>
       <c r="AN5" t="n">
@@ -1169,7 +1109,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # tallåga, grov, yxhuggen, gammal</t>
+          <t>1 substratenheter # gammal grov tallstock</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1191,15 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>75330797</v>
+        <v>75330799</v>
       </c>
       <c r="B6" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1231,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575516.2040151422</v>
+        <v>575438</v>
       </c>
       <c r="R6" t="n">
-        <v>7086891.861098818</v>
+        <v>7087023</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1264,19 +1199,9 @@
           <t>2017-10-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-10-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,7 +1223,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal grov, fallen torraka</t>
+          <t>1 substratenheter # tallåga, bränd, gammal</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 61417-2021 artfynd.xlsx
+++ b/artfynd/A 61417-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75330797</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75330800</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75330796</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75330798</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,8 +1267,20 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75330799</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>